--- a/exploratory_data_analisys/normalization/risultati/statistiche_descrittive.xlsx
+++ b/exploratory_data_analisys/normalization/risultati/statistiche_descrittive.xlsx
@@ -425,76 +425,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>IslandArea</t>
+          <t>Densità_pop</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Densità_pop</t>
+          <t>evi</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>evi</t>
+          <t>eolico</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>eolico</t>
+          <t>eolico_std</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>eolico_std</t>
+          <t>offshore</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>offshore</t>
+          <t>gdp_pro_capite</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>gdp_pro_capite</t>
+          <t>geothermal_potential</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>geothermal_potential</t>
+          <t>hydro</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>hydro</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>temp</t>
+          <t>solar_pow</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>solar_pow</t>
+          <t>solar_seas_ind</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>solar_seas_ind</t>
+          <t>superficie_res</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>superficie_res</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>gdp_pop_urban_merged</t>
         </is>
@@ -545,9 +540,6 @@
       <c r="N2" t="n">
         <v>2736</v>
       </c>
-      <c r="O2" t="n">
-        <v>2736</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -556,46 +548,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09937923216073431</v>
+        <v>-0.00330845010120375</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.00330845010120375</v>
+        <v>0.02868790198811602</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02868790198811602</v>
+        <v>2.475556005694149</v>
       </c>
       <c r="E3" t="n">
-        <v>2.475556005694149</v>
+        <v>0.04949192926291828</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04949192926291828</v>
+        <v>0.7048610245645277</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7048610245645277</v>
+        <v>0.01275754047808045</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01275754047808045</v>
+        <v>0.4654470863229462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4654470863229462</v>
+        <v>0.6398084817995293</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6398084817995293</v>
+        <v>-0.434305894455277</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.434305894455277</v>
+        <v>6.725080162906959</v>
       </c>
       <c r="L3" t="n">
-        <v>6.725080162906959</v>
+        <v>0.7669533450485546</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7669533450485546</v>
+        <v>0.1704714496482679</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1445258207495332</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.5687745778311922</v>
+        <v>0.5687745778309519</v>
       </c>
     </row>
     <row r="4">
@@ -605,46 +594,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7500430700516459</v>
+        <v>0.7395167307447567</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7395167307447567</v>
+        <v>0.6758574937639199</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6758574937639199</v>
+        <v>1.000182798648817</v>
       </c>
       <c r="E4" t="n">
+        <v>0.7177171554699632</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.000182798648817</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.7177171554699632</v>
-      </c>
       <c r="G4" t="n">
+        <v>0.5687015253253199</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.225390509752524</v>
+      </c>
+      <c r="I4" t="n">
         <v>1.000182798648817</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.5687015253253199</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.225390509752524</v>
-      </c>
       <c r="J4" t="n">
+        <v>0.7728073255540938</v>
+      </c>
+      <c r="K4" t="n">
         <v>1.000182798648817</v>
       </c>
-      <c r="K4" t="n">
-        <v>0.7728073255540938</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.000182798648817</v>
+        <v>2.096679500765967</v>
       </c>
       <c r="M4" t="n">
-        <v>2.096679500765967</v>
+        <v>0.7705897498813664</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6048408488550653</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.133905872665341</v>
+        <v>1.133905872664834</v>
       </c>
     </row>
     <row r="5">
@@ -654,46 +640,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.274145181978928</v>
+        <v>-2.164444264969734</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.164444264969734</v>
+        <v>-1.975753975960499</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.975753975960499</v>
+        <v>0.04105393391733923</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04105393391733923</v>
+        <v>-1.491698842407455</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.491698842407455</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-1.262995367947092</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.262995367947092</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-3.568235684758833</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.568235684758833</v>
+        <v>2.827575513919984</v>
       </c>
       <c r="L5" t="n">
-        <v>2.827575513919984</v>
+        <v>-0.6291031890723228</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6291031890723228</v>
+        <v>-1.04267808546002</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6759501735656157</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.2726798030937422</v>
+        <v>-0.2726798030937638</v>
       </c>
     </row>
     <row r="6">
@@ -703,46 +686,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4474432591226783</v>
+        <v>-0.5042094128856183</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.5042094128856183</v>
+        <v>-0.4659013701873879</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4659013701873879</v>
+        <v>1.71628596723711</v>
       </c>
       <c r="E6" t="n">
-        <v>1.71628596723711</v>
+        <v>-0.4884358951939276</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4884358951939276</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0.4630105751974706</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4630105751974706</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0.905870685627741</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.905870685627741</v>
+        <v>6.243681223297148</v>
       </c>
       <c r="L6" t="n">
-        <v>6.243681223297148</v>
+        <v>-0.2726231080661094</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2726231080661094</v>
+        <v>-0.3880472053978549</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3684048501006381</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.1961190336035212</v>
+        <v>-0.1961190336035349</v>
       </c>
     </row>
     <row r="7">
@@ -758,13 +738,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.502943905291837</v>
       </c>
       <c r="E7" t="n">
-        <v>2.502943905291837</v>
+        <v>-2.113110034174248e-16</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.113110034174248e-16</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -779,18 +759,15 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6.842600815937413</v>
       </c>
       <c r="L7" t="n">
-        <v>6.842600815937413</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.078975979200945e-16</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.025630077706069e-17</v>
-      </c>
-      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -801,46 +778,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5525567408773218</v>
+        <v>0.495790587114382</v>
       </c>
       <c r="C8" t="n">
-        <v>0.495790587114382</v>
+        <v>0.534098629812612</v>
       </c>
       <c r="D8" t="n">
-        <v>0.534098629812612</v>
+        <v>3.276578216855933</v>
       </c>
       <c r="E8" t="n">
-        <v>3.276578216855933</v>
+        <v>0.5115641048060722</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5115641048060722</v>
+        <v>1.363806556034006</v>
       </c>
       <c r="G8" t="n">
-        <v>1.363806556034006</v>
+        <v>0.5369894248025293</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5369894248025293</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.691052000626001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.691052000626001</v>
+        <v>0.09412931437225908</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09412931437225908</v>
+        <v>7.361183341188833</v>
       </c>
       <c r="L8" t="n">
-        <v>7.361183341188833</v>
+        <v>0.7273768919338909</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7273768919338909</v>
+        <v>0.6119527946021451</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6315951498993618</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.8038809663964788</v>
+        <v>0.8038809663964652</v>
       </c>
     </row>
     <row r="9">
@@ -850,46 +824,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.225025154451417</v>
+        <v>2.520047656869539</v>
       </c>
       <c r="C9" t="n">
-        <v>2.520047656869539</v>
+        <v>1.78836863764289</v>
       </c>
       <c r="D9" t="n">
-        <v>1.78836863764289</v>
+        <v>4.797180727742201</v>
       </c>
       <c r="E9" t="n">
-        <v>4.797180727742201</v>
+        <v>4.327048321695479</v>
       </c>
       <c r="F9" t="n">
-        <v>4.327048321695479</v>
+        <v>5.223578479449142</v>
       </c>
       <c r="G9" t="n">
-        <v>5.223578479449142</v>
+        <v>1.432710565685036</v>
       </c>
       <c r="H9" t="n">
-        <v>1.432710565685036</v>
+        <v>7.791347927064578</v>
       </c>
       <c r="I9" t="n">
-        <v>7.791347927064578</v>
+        <v>3.766131996926475</v>
       </c>
       <c r="J9" t="n">
-        <v>3.766131996926475</v>
+        <v>0.3500094728868549</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3500094728868549</v>
+        <v>9.294757365391712</v>
       </c>
       <c r="L9" t="n">
-        <v>9.294757365391712</v>
+        <v>18.04337229932958</v>
       </c>
       <c r="M9" t="n">
-        <v>18.04337229932958</v>
+        <v>4.026362644442906</v>
       </c>
       <c r="N9" t="n">
-        <v>1.300406345020206</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.311842167165813</v>
+        <v>3.311842167163709</v>
       </c>
     </row>
   </sheetData>
